--- a/data/2026/cjsl/fall/albion-sc-brooklyn-b13-14-premier-williamsburg.xlsx
+++ b/data/2026/cjsl/fall/albion-sc-brooklyn-b13-14-premier-williamsburg.xlsx
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>
@@ -259,7 +259,7 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Canceled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/albion-sc-brooklyn-b13-14-premier-williamsburg.xlsx
+++ b/data/2026/cjsl/fall/albion-sc-brooklyn-b13-14-premier-williamsburg.xlsx
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4 - 2</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/albion-sc-brooklyn-b13-14-premier-williamsburg.xlsx
+++ b/data/2026/cjsl/fall/albion-sc-brooklyn-b13-14-premier-williamsburg.xlsx
@@ -329,7 +329,7 @@
       </c>
       <c r="E6" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8 - 0</t>
         </is>
       </c>
       <c r="F6" s="0" t="inlineStr">
